--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\DA_ads-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC2A41F-8F94-4816-B372-C4093DEC5EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5E2815-847B-452A-8A4B-498938515FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
@@ -869,7 +869,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1454161</v>
+        <v>4045073</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\DA_ads-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5E2815-847B-452A-8A4B-498938515FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB2ABAE-3AF4-41ED-B6FB-BDE97E312F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
   <si>
     <t>업체명</t>
   </si>
@@ -252,6 +252,29 @@
   </si>
   <si>
     <t>시종도어 GFA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미혜</t>
+  </si>
+  <si>
+    <t>비에스방수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이즈코리아</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>승훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메디컬티비</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -648,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -888,21 +911,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B22">
-        <v>1632478</v>
+        <v>467737</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B23">
-        <v>3300114</v>
+        <v>1632478</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -910,10 +933,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>207750</v>
+        <v>3300114</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
@@ -921,10 +944,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>3113312</v>
+        <v>207750</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
@@ -932,10 +955,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
-        <v>2404793</v>
+        <v>3113312</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -943,10 +966,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="B27">
-        <v>1617009</v>
+        <v>2404793</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
@@ -954,10 +977,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28">
-        <v>1319465</v>
+        <v>1617009</v>
       </c>
       <c r="C28" t="s">
         <v>22</v>
@@ -965,10 +988,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29">
-        <v>2694228</v>
+        <v>1319465</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -976,10 +999,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B30">
-        <v>4165324</v>
+        <v>2694228</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
@@ -987,10 +1010,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31">
-        <v>634844</v>
+        <v>4165324</v>
       </c>
       <c r="C31" t="s">
         <v>22</v>
@@ -998,10 +1021,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B32">
-        <v>1340565</v>
+        <v>634844</v>
       </c>
       <c r="C32" t="s">
         <v>22</v>
@@ -1009,43 +1032,43 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B33">
-        <v>530852</v>
+        <v>1340565</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B34">
-        <v>2760916</v>
+        <v>3492381</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B35">
-        <v>3217504</v>
+        <v>530852</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B36">
-        <v>2378803</v>
+        <v>2760916</v>
       </c>
       <c r="C36" t="s">
         <v>52</v>
@@ -1053,10 +1076,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B37">
-        <v>3124482</v>
+        <v>3217504</v>
       </c>
       <c r="C37" t="s">
         <v>52</v>
@@ -1064,10 +1087,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B38">
-        <v>222411</v>
+        <v>2378803</v>
       </c>
       <c r="C38" t="s">
         <v>52</v>
@@ -1075,10 +1098,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B39">
-        <v>1892757</v>
+        <v>3124482</v>
       </c>
       <c r="C39" t="s">
         <v>52</v>
@@ -1086,10 +1109,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B40">
-        <v>2886394</v>
+        <v>222411</v>
       </c>
       <c r="C40" t="s">
         <v>52</v>
@@ -1097,10 +1120,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B41">
-        <v>2697039</v>
+        <v>1892757</v>
       </c>
       <c r="C41" t="s">
         <v>52</v>
@@ -1108,43 +1131,43 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B42">
-        <v>1229073</v>
+        <v>2886394</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B43">
-        <v>1800688</v>
+        <v>2697039</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="B44">
-        <v>607620</v>
+        <v>3615396</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B45">
-        <v>4180383</v>
+        <v>1229073</v>
       </c>
       <c r="C45" t="s">
         <v>53</v>
@@ -1152,10 +1175,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B46">
-        <v>3536711</v>
+        <v>1800688</v>
       </c>
       <c r="C46" t="s">
         <v>53</v>
@@ -1163,10 +1186,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B47">
-        <v>3076410</v>
+        <v>607620</v>
       </c>
       <c r="C47" t="s">
         <v>53</v>
@@ -1174,10 +1197,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B48">
-        <v>3370005</v>
+        <v>4180383</v>
       </c>
       <c r="C48" t="s">
         <v>53</v>
@@ -1185,10 +1208,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B49">
-        <v>2310274</v>
+        <v>3536711</v>
       </c>
       <c r="C49" t="s">
         <v>53</v>
@@ -1196,10 +1219,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B50">
-        <v>1875332</v>
+        <v>3076410</v>
       </c>
       <c r="C50" t="s">
         <v>53</v>
@@ -1207,10 +1230,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B51">
-        <v>3062481</v>
+        <v>3370005</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
@@ -1218,10 +1241,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B52">
-        <v>3259223</v>
+        <v>2310274</v>
       </c>
       <c r="C52" t="s">
         <v>53</v>
@@ -1229,10 +1252,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B53">
-        <v>3459602</v>
+        <v>1875332</v>
       </c>
       <c r="C53" t="s">
         <v>53</v>
@@ -1240,10 +1263,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B54">
-        <v>4005081</v>
+        <v>3062481</v>
       </c>
       <c r="C54" t="s">
         <v>53</v>
@@ -1251,10 +1274,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B55">
-        <v>2901614</v>
+        <v>3259223</v>
       </c>
       <c r="C55" t="s">
         <v>53</v>
@@ -1262,10 +1285,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B56">
-        <v>3325314</v>
+        <v>3459602</v>
       </c>
       <c r="C56" t="s">
         <v>53</v>
@@ -1273,12 +1296,45 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57">
+        <v>4005081</v>
+      </c>
+      <c r="C57" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58">
+        <v>2901614</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59">
+        <v>3325314</v>
+      </c>
+      <c r="C59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>51</v>
       </c>
-      <c r="B57">
+      <c r="B60">
         <v>607620</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C60" t="s">
         <v>53</v>
       </c>
     </row>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB2ABAE-3AF4-41ED-B6FB-BDE97E312F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C392B59D-986F-459B-B2E7-DF4803F03F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="43185" yWindow="2250" windowWidth="28845" windowHeight="16650" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1156,7 +1156,7 @@
         <v>68</v>
       </c>
       <c r="B44">
-        <v>3615396</v>
+        <v>1264154</v>
       </c>
       <c r="C44" t="s">
         <v>67</v>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\123\DA_ads-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C392B59D-986F-459B-B2E7-DF4803F03F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB2EEF2-35B3-4CD8-A47A-7BED5F73486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43185" yWindow="2250" windowWidth="28845" windowHeight="16650" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="73">
   <si>
     <t>업체명</t>
   </si>
@@ -275,6 +275,14 @@
   </si>
   <si>
     <t>메디컬티비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>승훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여수카멜리아</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -671,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -691,655 +699,670 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>3469289</v>
+        <v>1632478</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>420332</v>
+        <v>3300114</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>1346816</v>
+        <v>207750</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>1973823</v>
+        <v>3113312</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>360788</v>
+        <v>2404793</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>3337700</v>
+        <v>1617009</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B8">
-        <v>2920327</v>
+        <v>1319465</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B9">
-        <v>4008088</v>
+        <v>2694228</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B10">
-        <v>464459</v>
+        <v>4165324</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B11">
-        <v>4107446</v>
+        <v>634844</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>366371</v>
+        <v>1340565</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B13">
-        <v>2886931</v>
+        <v>3492381</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>1454161</v>
+        <v>1229073</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <v>3290345</v>
+        <v>1800688</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>2612915</v>
+        <v>607620</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>3324981</v>
+        <v>4180383</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B18">
-        <v>3124325</v>
+        <v>3536711</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B19">
-        <v>2924114</v>
+        <v>3076410</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B20">
-        <v>4045073</v>
+        <v>3370005</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B21">
-        <v>3322328</v>
+        <v>2310274</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B22">
-        <v>467737</v>
+        <v>1875332</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>1632478</v>
+        <v>3062481</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B24">
-        <v>3300114</v>
+        <v>3259223</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B25">
-        <v>207750</v>
+        <v>3459602</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B26">
-        <v>3113312</v>
+        <v>4005081</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B27">
-        <v>2404793</v>
+        <v>2901614</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B28">
-        <v>1617009</v>
+        <v>3325314</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B29">
-        <v>1319465</v>
+        <v>607620</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="B30">
-        <v>2694228</v>
+        <v>3469289</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="B31">
-        <v>4165324</v>
+        <v>420332</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B32">
-        <v>634844</v>
+        <v>1346816</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B33">
-        <v>1340565</v>
+        <v>1973823</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B34">
-        <v>3492381</v>
+        <v>360788</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B35">
-        <v>530852</v>
+        <v>3337700</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="B36">
-        <v>2760916</v>
+        <v>2920327</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="B37">
-        <v>3217504</v>
+        <v>4008088</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B38">
-        <v>2378803</v>
+        <v>464459</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>3124482</v>
+        <v>4107446</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B40">
-        <v>222411</v>
+        <v>366371</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B41">
-        <v>1892757</v>
+        <v>2886931</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B42">
-        <v>2886394</v>
+        <v>1454161</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B43">
-        <v>2697039</v>
+        <v>3290345</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B44">
-        <v>1264154</v>
+        <v>2612915</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B45">
-        <v>1229073</v>
+        <v>3324981</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B46">
-        <v>1800688</v>
+        <v>3124325</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B47">
-        <v>607620</v>
+        <v>2924114</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B48">
-        <v>4180383</v>
+        <v>4045073</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B49">
-        <v>3536711</v>
+        <v>3322328</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B50">
-        <v>3076410</v>
+        <v>467737</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B51">
-        <v>3370005</v>
+        <v>3880428</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B52">
-        <v>2310274</v>
+        <v>530852</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B53">
-        <v>1875332</v>
+        <v>2760916</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B54">
-        <v>3062481</v>
+        <v>3217504</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B55">
-        <v>3259223</v>
+        <v>2378803</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B56">
-        <v>3459602</v>
+        <v>3124482</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B57">
-        <v>4005081</v>
+        <v>222411</v>
       </c>
       <c r="C57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B58">
-        <v>2901614</v>
+        <v>1892757</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B59">
-        <v>3325314</v>
+        <v>2886394</v>
       </c>
       <c r="C59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B60">
-        <v>607620</v>
+        <v>2697039</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61">
+        <v>1264154</v>
+      </c>
+      <c r="C61" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C52" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}"/>
+  <autoFilter ref="A1:C52" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C61">
+      <sortCondition ref="C1:C52"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\123\DA_ads-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB2EEF2-35B3-4CD8-A47A-7BED5F73486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D111DCF-CAA6-4785-A970-A485A0AAFD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
   <si>
     <t>업체명</t>
   </si>
@@ -283,6 +283,14 @@
   </si>
   <si>
     <t>여수카멜리아</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미혜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>개똥이네</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -679,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1355,6 +1363,17 @@
       </c>
       <c r="C61" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62">
+        <v>406051</v>
+      </c>
+      <c r="C62" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D111DCF-CAA6-4785-A970-A485A0AAFD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403652B7-0F48-44CB-9108-3773EA86833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
   <si>
     <t>업체명</t>
   </si>
@@ -101,10 +101,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>더마드라이 GFA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>담당자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -239,7 +235,22 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>한우이츠 GFA</t>
+    <t>시종도어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미혜</t>
+  </si>
+  <si>
+    <t>비에스방수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이즈코리아</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -247,50 +258,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>시종도어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>시종도어 GFA</t>
+    <t>메디컬티비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>승훈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여수카멜리아</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>미혜</t>
-  </si>
-  <si>
-    <t>비에스방수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤이즈코리아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>승훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>메디컬티비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>승훈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>여수카멜리아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미혜</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>개똥이네</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로베라</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -702,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -713,271 +701,271 @@
         <v>1632478</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>3300114</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>207750</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>3113312</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>2404793</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>1617009</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8">
         <v>1319465</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9">
         <v>2694228</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10">
         <v>4165324</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>634844</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>1340565</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>3492381</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14">
         <v>1229073</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <v>1800688</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>607620</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17">
         <v>4180383</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18">
         <v>3536711</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19">
         <v>3076410</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20">
         <v>3370005</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21">
         <v>2310274</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22">
         <v>1875332</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <v>3062481</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24">
         <v>3259223</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25">
         <v>3459602</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B26">
-        <v>4005081</v>
+        <v>2901614</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -985,10 +973,10 @@
         <v>49</v>
       </c>
       <c r="B27">
-        <v>2901614</v>
+        <v>3325314</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -996,390 +984,365 @@
         <v>50</v>
       </c>
       <c r="B28">
-        <v>3325314</v>
+        <v>607620</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="B29">
-        <v>607620</v>
+        <v>3469289</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30">
-        <v>3469289</v>
+        <v>420332</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31">
-        <v>420332</v>
+        <v>1346816</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32">
-        <v>1346816</v>
+        <v>1973823</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33">
-        <v>1973823</v>
+        <v>360788</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34">
-        <v>360788</v>
+        <v>3337700</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="B35">
-        <v>3337700</v>
+        <v>2920327</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B36">
-        <v>2920327</v>
+        <v>464459</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B37">
-        <v>4008088</v>
+        <v>4107446</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B38">
-        <v>464459</v>
+        <v>366371</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B39">
-        <v>4107446</v>
+        <v>2886931</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B40">
-        <v>366371</v>
+        <v>1454161</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B41">
-        <v>2886931</v>
+        <v>3290345</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B42">
-        <v>1454161</v>
+        <v>2612915</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B43">
-        <v>3290345</v>
+        <v>3324981</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B44">
-        <v>2612915</v>
+        <v>3124325</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B45">
-        <v>3324981</v>
+        <v>2924114</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B46">
-        <v>3124325</v>
+        <v>3322328</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="B47">
-        <v>2924114</v>
+        <v>467737</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="B48">
-        <v>4045073</v>
+        <v>3880428</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B49">
-        <v>3322328</v>
+        <v>530852</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="B50">
-        <v>467737</v>
+        <v>2760916</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="B51">
-        <v>3880428</v>
+        <v>3217504</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B52">
-        <v>530852</v>
+        <v>2378803</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B53">
-        <v>2760916</v>
+        <v>3124482</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B54">
-        <v>3217504</v>
+        <v>222411</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B55">
-        <v>2378803</v>
+        <v>1892757</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B56">
-        <v>3124482</v>
+        <v>2886394</v>
       </c>
       <c r="C56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B57">
-        <v>222411</v>
+        <v>2697039</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B58">
-        <v>1892757</v>
+        <v>1264154</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B59">
-        <v>2886394</v>
+        <v>406051</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B60">
-        <v>2697039</v>
-      </c>
-      <c r="C60" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61">
-        <v>1264154</v>
-      </c>
-      <c r="C61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62">
-        <v>406051</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
+        <v>1325932</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C52" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C61">
-      <sortCondition ref="C1:C52"/>
+  <autoFilter ref="A1:C49" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C58">
+      <sortCondition ref="C1:C49"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403652B7-0F48-44CB-9108-3773EA86833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A77FE6B-2C46-43A4-AE35-2BA93EA481E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="8865" yWindow="2385" windowWidth="28845" windowHeight="16650" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
   <si>
     <t>업체명</t>
   </si>
@@ -279,6 +279,26 @@
   </si>
   <si>
     <t>로베라</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한우이츠 GFA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시종도어 GFA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더마드라이 GFA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로베라 GFA</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -675,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1337,6 +1357,53 @@
       </c>
       <c r="B60">
         <v>1325932</v>
+      </c>
+      <c r="C60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61">
+        <v>4005081</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62">
+        <v>4008088</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63">
+        <v>4045073</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64">
+        <v>3565449</v>
+      </c>
+      <c r="C64" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A77FE6B-2C46-43A4-AE35-2BA93EA481E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E29CFCA-8502-4ABF-8EEB-A461AE78AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8865" yWindow="2385" windowWidth="28845" windowHeight="16650" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <t>업체명</t>
   </si>
@@ -279,10 +279,6 @@
   </si>
   <si>
     <t>로베라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미정</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -695,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1359,29 +1355,29 @@
         <v>1325932</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B61">
-        <v>4005081</v>
+        <v>3565449</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B62">
-        <v>4008088</v>
+        <v>1325932</v>
       </c>
       <c r="C62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1389,21 +1385,43 @@
         <v>75</v>
       </c>
       <c r="B63">
-        <v>4045073</v>
+        <v>3565449</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B64">
-        <v>3565449</v>
+        <v>4005081</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65">
+        <v>4008088</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66">
+        <v>4045073</v>
+      </c>
+      <c r="C66" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E29CFCA-8502-4ABF-8EEB-A461AE78AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4E0D3F-00CD-4C06-B379-89CFADFD407D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>업체명</t>
   </si>
@@ -691,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1371,56 +1374,34 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B62">
-        <v>1325932</v>
+        <v>4005081</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B63">
-        <v>3565449</v>
+        <v>4008088</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B64">
-        <v>4005081</v>
+        <v>4045073</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65">
-        <v>4008088</v>
-      </c>
-      <c r="C65" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66">
-        <v>4045073</v>
-      </c>
-      <c r="C66" t="s">
         <v>20</v>
       </c>
     </row>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4E0D3F-00CD-4C06-B379-89CFADFD407D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D61E26F-6011-4724-837B-C23602B55B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{343BCD55-24DB-40A3-BB28-6EC14438406C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>업체명</t>
   </si>
@@ -100,10 +97,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>가이드맨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>담당자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -112,151 +105,13 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>미혜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>키들</t>
   </si>
   <si>
-    <t>청주오스코</t>
-  </si>
-  <si>
-    <t>리틀코리아</t>
-  </si>
-  <si>
-    <t>부성에이티</t>
-  </si>
-  <si>
-    <t>컨텍스쳐</t>
-  </si>
-  <si>
-    <t>아틀라시안</t>
-  </si>
-  <si>
-    <t>이유즈</t>
-  </si>
-  <si>
-    <t>수협보험</t>
-  </si>
-  <si>
-    <t>네모조명</t>
-  </si>
-  <si>
-    <t>아뜰리에구리</t>
-  </si>
-  <si>
-    <t>건우씨엔에스</t>
-  </si>
-  <si>
-    <t>IDS코리아</t>
-  </si>
-  <si>
-    <t>DB INC</t>
-  </si>
-  <si>
-    <t>생생어르신복지센터</t>
-  </si>
-  <si>
-    <t>알톤</t>
-  </si>
-  <si>
-    <t>더드림핑</t>
-  </si>
-  <si>
-    <t>한양패키지</t>
-  </si>
-  <si>
-    <t>펫츠비통</t>
-  </si>
-  <si>
-    <t>해피발스데이</t>
-  </si>
-  <si>
-    <t>휴앤고</t>
-  </si>
-  <si>
-    <t>굿데이 남북결혼</t>
-  </si>
-  <si>
-    <t>판타스틱코인노래방</t>
-  </si>
-  <si>
-    <t>머크코리아 1-1</t>
-  </si>
-  <si>
-    <t>머크코리아 2-1</t>
-  </si>
-  <si>
-    <t>머크코리아 3-1</t>
-  </si>
-  <si>
-    <t>한우이츠</t>
-  </si>
-  <si>
-    <t>일두</t>
-  </si>
-  <si>
-    <t>신한라이프케어</t>
-  </si>
-  <si>
-    <t>SK텔레콤</t>
-  </si>
-  <si>
-    <t>정인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>민아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국카드시스템</t>
-  </si>
-  <si>
-    <t>더피플</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CS H&amp;L 행정사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>속편한철거</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>크림미술학원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대성소파</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시종도어</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>미혜</t>
-  </si>
-  <si>
-    <t>비에스방수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤이즈코리아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>승훈</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -273,22 +128,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>미혜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>개똥이네</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>로베라</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>한우이츠 GFA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시종도어 GFA</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -299,6 +142,15 @@
   <si>
     <t>로베라 GFA</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금호주택</t>
+  </si>
+  <si>
+    <t>뷰티반려문화</t>
+  </si>
+  <si>
+    <t>집콕</t>
   </si>
 </sst>
 </file>
@@ -694,7 +546,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
-  <dimension ref="A1:C64"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -709,306 +562,36 @@
         <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2">
-        <v>1632478</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
-        <v>3300114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>207750</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5">
-        <v>3113312</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
-        <v>2404793</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7">
-        <v>1617009</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8">
-        <v>1319465</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9">
-        <v>2694228</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10">
-        <v>4165324</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11">
-        <v>634844</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>1340565</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13">
-        <v>3492381</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14">
-        <v>1229073</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15">
-        <v>1800688</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16">
-        <v>607620</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17">
-        <v>4180383</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18">
-        <v>3536711</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19">
-        <v>3076410</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20">
-        <v>3370005</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21">
-        <v>2310274</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22">
-        <v>1875332</v>
-      </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23">
-        <v>3062481</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24">
-        <v>3259223</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25">
-        <v>3459602</v>
-      </c>
-      <c r="C25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26">
-        <v>2901614</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27">
-        <v>3325314</v>
-      </c>
-      <c r="C27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28">
-        <v>607620</v>
-      </c>
-      <c r="C28" t="s">
-        <v>52</v>
-      </c>
-    </row>
+    </row>
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1</v>
@@ -1017,7 +600,7 @@
         <v>3469289</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -1028,7 +611,7 @@
         <v>420332</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -1039,7 +622,7 @@
         <v>1346816</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1050,7 +633,7 @@
         <v>1973823</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1061,7 +644,7 @@
         <v>360788</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1072,18 +655,18 @@
         <v>3337700</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B35">
         <v>2920327</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1094,7 +677,7 @@
         <v>464459</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1105,7 +688,7 @@
         <v>4107446</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1116,7 +699,7 @@
         <v>366371</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1127,7 +710,7 @@
         <v>2886931</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1138,7 +721,7 @@
         <v>1454161</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1149,7 +732,7 @@
         <v>3290345</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1160,7 +743,7 @@
         <v>2612915</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1171,7 +754,7 @@
         <v>3324981</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1182,7 +765,7 @@
         <v>3124325</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -1193,220 +776,138 @@
         <v>2924114</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>3322328</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="B47">
         <v>467737</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="B48">
         <v>3880428</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49">
-        <v>530852</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>28</v>
-      </c>
-      <c r="B50">
-        <v>2760916</v>
-      </c>
-      <c r="C50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51">
-        <v>3217504</v>
-      </c>
-      <c r="C51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52">
-        <v>2378803</v>
-      </c>
-      <c r="C52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53">
-        <v>3124482</v>
-      </c>
-      <c r="C53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>32</v>
-      </c>
-      <c r="B54">
-        <v>222411</v>
-      </c>
-      <c r="C54" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>33</v>
-      </c>
-      <c r="B55">
-        <v>1892757</v>
-      </c>
-      <c r="C55" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56">
-        <v>2886394</v>
-      </c>
-      <c r="C56" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57">
-        <v>2697039</v>
-      </c>
-      <c r="C57" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58">
-        <v>1264154</v>
-      </c>
-      <c r="C58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>70</v>
-      </c>
-      <c r="B59">
-        <v>406051</v>
-      </c>
-      <c r="C59" t="s">
-        <v>69</v>
-      </c>
-    </row>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B60">
         <v>1325932</v>
       </c>
       <c r="C60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B61">
         <v>3565449</v>
       </c>
       <c r="C61" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>72</v>
-      </c>
-      <c r="B62">
-        <v>4005081</v>
-      </c>
-      <c r="C62" t="s">
-        <v>52</v>
-      </c>
-    </row>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="B63">
         <v>4008088</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="B64">
         <v>4045073</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B65">
+        <v>2550342</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66">
+        <v>4335571</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67">
+        <v>3492778</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C49" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
+  <autoFilter ref="A1:C64" xr:uid="{FAD8DF0E-B4B7-415A-A8DA-946DB4D6F0B8}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C58">
       <sortCondition ref="C1:C49"/>
     </sortState>
